--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.26.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.26.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.26" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.26.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.26.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0026.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0026.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -807,7 +807,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.26.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.26.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.26" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="39" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -599,18 +599,18 @@
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: a subpo Ã¦ ena may issue under the seal of this Honorable</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The form is as follows :â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]19</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]19</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 19</t>
@@ -618,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L14: isolated marker/symbol line :: 1</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]19</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -661,7 +661,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”8. The</t>
+          <t>L87: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • and con-</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -669,13 +669,17 @@
       <c r="N3" s="1" t="inlineStr"/>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L16: isolated marker/symbol line :: 1</t>
+          <t>L14: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L87: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • and con-</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -706,15 +710,15 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ and con-</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr"/>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L16: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
@@ -734,12 +738,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -929,12 +933,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -973,7 +977,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1012,7 +1016,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1090,7 +1094,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
